--- a/時間（じかん）.xlsx
+++ b/時間（じかん）.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A89913-7434-477F-9B08-EE596537B461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A58595-E4F7-4AB6-BCF3-10029B1B38D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="基礎（きそ）" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
+    <sheet name="比較「ひかく」" sheetId="4" r:id="rId2"/>
     <sheet name="期日（きじつ）" sheetId="3" r:id="rId3"/>
     <sheet name="古代（こだい）" sheetId="5" r:id="rId4"/>
     <sheet name="星座（せいざ）" sheetId="6" r:id="rId5"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="448">
   <si>
     <t>明日</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2288,39 +2288,6 @@
   <si>
     <t>新世紀｜しんせいき</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新歴代｜しんれきだい</t>
-  </si>
-  <si>
-    <t>新時差｜しんじさ</t>
-  </si>
-  <si>
-    <t>新将来｜しんしょうらい</t>
-  </si>
-  <si>
-    <t>新未来｜しんみらい</t>
-  </si>
-  <si>
-    <t>新長期｜しんちょうき</t>
-  </si>
-  <si>
-    <t>新短期｜しんたんき</t>
-  </si>
-  <si>
-    <t>新前期｜しんぜんき</t>
-  </si>
-  <si>
-    <t>新後期｜しんこうき</t>
-  </si>
-  <si>
-    <t>新最古｜しんさいこ</t>
-  </si>
-  <si>
-    <t>新最近｜しんさいきん</t>
-  </si>
-  <si>
-    <t>新期間｜しんきかん</t>
   </si>
 </sst>
 </file>
